--- a/stat_arb/comp_stats_2026/lt_tsy2_comp_stats_2026.xlsx
+++ b/stat_arb/comp_stats_2026/lt_tsy2_comp_stats_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-crypto\crypto-project\stat_arb\comp_stats_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E84A5E-BB88-4305-B037-7FBF258C1649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9653ECA-6F2B-4854-89F0-E8D67BD8A72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="18684" windowHeight="10452" firstSheet="3" activeTab="3" xr2:uid="{156AA4A9-4121-45E5-84BA-9802D189ED0E}"/>
+    <workbookView xWindow="31140" yWindow="1965" windowWidth="20790" windowHeight="14235" firstSheet="2" activeTab="5" xr2:uid="{F46FAC0E-0041-4624-9DA5-82A8C2997FF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Results Table" sheetId="1" r:id="rId1"/>
@@ -249,14 +249,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,20 +275,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -626,15 +616,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D807EC-0813-464F-85F4-F82883710794}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D083292-6977-434B-866A-0BBDD3951B67}">
   <dimension ref="A1:BD10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="56" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="56" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +791,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -971,7 +961,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1141,857 +1131,857 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
       <c r="B4">
-        <v>-277.00500000000022</v>
+        <v>287.63000000009271</v>
       </c>
       <c r="C4">
-        <v>-207.8950000000201</v>
+        <v>386.00000000009095</v>
       </c>
       <c r="D4">
-        <v>-316.77500000002817</v>
+        <v>392.52000000009639</v>
       </c>
       <c r="E4">
-        <v>-233.22500000000616</v>
+        <v>594.42000000005623</v>
       </c>
       <c r="F4">
-        <v>-342.10500000001423</v>
+        <v>612.50000000004343</v>
       </c>
       <c r="G4">
-        <v>-377.62500000001683</v>
+        <v>530.87000000005389</v>
       </c>
       <c r="H4">
-        <v>-517.01500000000908</v>
+        <v>546.88000000004979</v>
       </c>
       <c r="I4">
-        <v>-517.01500000000908</v>
+        <v>564.96000000003687</v>
       </c>
       <c r="J4">
-        <v>-499.31500000001824</v>
+        <v>481.38000000003279</v>
       </c>
       <c r="K4">
-        <v>-363.46500000000839</v>
+        <v>567.18000000003485</v>
       </c>
       <c r="L4">
-        <v>-491.57500000000789</v>
+        <v>590.9400000000503</v>
       </c>
       <c r="M4">
-        <v>-491.57500000000789</v>
+        <v>683.92000000003361</v>
       </c>
       <c r="N4">
-        <v>-473.87500000001694</v>
+        <v>600.34000000002959</v>
       </c>
       <c r="O4">
-        <v>-338.02500000000714</v>
+        <v>686.14000000003159</v>
       </c>
       <c r="P4">
-        <v>-448.61500000000012</v>
+        <v>584.68000000000882</v>
       </c>
       <c r="Q4">
-        <v>-461.09500000000799</v>
+        <v>571.28000000006477</v>
       </c>
       <c r="R4">
-        <v>-461.09500000000799</v>
+        <v>674.50000000004411</v>
       </c>
       <c r="S4">
-        <v>-443.39500000001715</v>
+        <v>607.46000000002664</v>
       </c>
       <c r="T4">
-        <v>-307.54500000000735</v>
+        <v>698.71000000001902</v>
       </c>
       <c r="U4">
-        <v>-418.13500000000045</v>
+        <v>640.25999999999624</v>
       </c>
       <c r="V4">
-        <v>-301.07499999999777</v>
+        <v>535.02999999999281</v>
       </c>
       <c r="W4">
-        <v>-426.96500000000674</v>
+        <v>445.66000000003567</v>
       </c>
       <c r="X4">
-        <v>-426.96500000000674</v>
+        <v>355.35000000000866</v>
       </c>
       <c r="Y4">
-        <v>-409.2650000000159</v>
+        <v>271.77000000000453</v>
       </c>
       <c r="Z4">
-        <v>-273.4150000000061</v>
+        <v>363.01999999999703</v>
       </c>
       <c r="AA4">
-        <v>-365.8749999999992</v>
+        <v>304.5699999999743</v>
       </c>
       <c r="AB4">
-        <v>-248.81499999999653</v>
+        <v>233.0899999999786</v>
       </c>
       <c r="AC4">
-        <v>-224.73499999999558</v>
+        <v>121.48999999996664</v>
       </c>
       <c r="AD4">
-        <v>-345.62499999999159</v>
+        <v>497.69000000005383</v>
       </c>
       <c r="AE4">
-        <v>-345.62499999999159</v>
+        <v>407.38000000002671</v>
       </c>
       <c r="AF4">
-        <v>-327.92500000000064</v>
+        <v>316.92000000001309</v>
       </c>
       <c r="AG4">
-        <v>-192.07499999999084</v>
+        <v>408.17000000000553</v>
       </c>
       <c r="AH4">
-        <v>-284.53499999998394</v>
+        <v>349.71999999998275</v>
       </c>
       <c r="AI4">
-        <v>-167.47499999998126</v>
+        <v>278.23999999998716</v>
       </c>
       <c r="AJ4">
-        <v>-131.87499999998056</v>
+        <v>288.28999999999019</v>
       </c>
       <c r="AK4">
-        <v>-165.87500000000097</v>
+        <v>438.60999999998575</v>
       </c>
       <c r="AL4">
-        <v>-366.54499999999496</v>
+        <v>636.64000000006831</v>
       </c>
       <c r="AM4">
-        <v>-366.54499999999496</v>
+        <v>546.33000000004131</v>
       </c>
       <c r="AN4">
-        <v>-246.36499999998364</v>
+        <v>467.53000000004209</v>
       </c>
       <c r="AO4">
-        <v>-110.5149999999739</v>
+        <v>352.74000000002104</v>
       </c>
       <c r="AP4">
-        <v>-202.974999999967</v>
+        <v>294.28999999999826</v>
       </c>
       <c r="AQ4">
-        <v>7.4250000000269551</v>
+        <v>199.5099999999909</v>
       </c>
       <c r="AR4">
-        <v>76.565000000027794</v>
+        <v>209.55999999999392</v>
       </c>
       <c r="AS4">
-        <v>58.955000000014991</v>
+        <v>359.87999999998954</v>
       </c>
       <c r="AT4">
-        <v>121.90500000003158</v>
+        <v>309.12999999994781</v>
       </c>
       <c r="AU4">
-        <v>-227.38499999996645</v>
+        <v>598.6500000000708</v>
       </c>
       <c r="AV4">
-        <v>-331.76499999998231</v>
+        <v>460.71000000005023</v>
       </c>
       <c r="AW4">
-        <v>-211.58499999997088</v>
+        <v>425.56000000005366</v>
       </c>
       <c r="AX4">
-        <v>-75.734999999961133</v>
+        <v>310.77000000003255</v>
       </c>
       <c r="AY4">
-        <v>-56.314999999959468</v>
+        <v>205.96000000002829</v>
       </c>
       <c r="AZ4">
-        <v>25.05500000003218</v>
+        <v>111.18000000002084</v>
       </c>
       <c r="BA4">
-        <v>94.195000000033133</v>
+        <v>100.88000000001978</v>
       </c>
       <c r="BB4">
-        <v>131.96500000004096</v>
+        <v>251.20000000001534</v>
       </c>
       <c r="BC4">
-        <v>144.80500000005048</v>
+        <v>200.44999999997356</v>
       </c>
       <c r="BD4">
-        <v>373.84500000003447</v>
-      </c>
-    </row>
-    <row r="5" spans="1:56" x14ac:dyDescent="0.3">
+        <v>25.029999999948245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
       <c r="B5">
-        <v>182288.64193548387</v>
+        <v>173150.39111940298</v>
       </c>
       <c r="C5">
-        <v>179062.8885483871</v>
+        <v>165685.91559701491</v>
       </c>
       <c r="D5">
-        <v>177450.7145967742</v>
+        <v>162700.41208955224</v>
       </c>
       <c r="E5">
-        <v>172610.88016129032</v>
+        <v>150761.50440298507</v>
       </c>
       <c r="F5">
-        <v>170998.70620967742</v>
+        <v>147777.08440298509</v>
       </c>
       <c r="G5">
-        <v>169386.1739516129</v>
+        <v>144791.84716417914</v>
       </c>
       <c r="H5">
-        <v>164546.09137096777</v>
+        <v>149269.47604477612</v>
       </c>
       <c r="I5">
-        <v>164546.09137096777</v>
+        <v>146285.05604477614</v>
       </c>
       <c r="J5">
-        <v>161321.61911290322</v>
+        <v>141807.51925373133</v>
       </c>
       <c r="K5">
-        <v>159708.33201612905</v>
+        <v>137329.11246268658</v>
       </c>
       <c r="L5">
-        <v>159706.08338709676</v>
+        <v>144792.88007462685</v>
       </c>
       <c r="M5">
-        <v>159706.08338709676</v>
+        <v>140314.68305970149</v>
       </c>
       <c r="N5">
-        <v>156481.61112903227</v>
+        <v>135837.14626865674</v>
       </c>
       <c r="O5">
-        <v>154868.32403225807</v>
+        <v>131358.73947761193</v>
       </c>
       <c r="P5">
-        <v>151641.3939516129</v>
+        <v>123894.77835820896</v>
       </c>
       <c r="Q5">
-        <v>159705.74</v>
+        <v>141808.59985074628</v>
       </c>
       <c r="R5">
-        <v>159705.74</v>
+        <v>134344.42932835821</v>
       </c>
       <c r="S5">
-        <v>156481.26774193547</v>
+        <v>129867.11268656717</v>
       </c>
       <c r="T5">
-        <v>154867.9806451613</v>
+        <v>123896.28186567164</v>
       </c>
       <c r="U5">
-        <v>151641.05056451613</v>
+        <v>116431.13895522388</v>
       </c>
       <c r="V5">
-        <v>146801.15532258066</v>
+        <v>113446.7306716418</v>
       </c>
       <c r="W5">
-        <v>159705.59967741935</v>
+        <v>132850.65305970149</v>
       </c>
       <c r="X5">
-        <v>159705.59967741935</v>
+        <v>125387.7210447761</v>
       </c>
       <c r="Y5">
-        <v>156481.12741935483</v>
+        <v>120910.18425373134</v>
       </c>
       <c r="Z5">
-        <v>154867.84032258068</v>
+        <v>114939.35343283582</v>
       </c>
       <c r="AA5">
-        <v>151640.91024193549</v>
+        <v>107474.21052238806</v>
       </c>
       <c r="AB5">
-        <v>146801.01499999998</v>
+        <v>104490.6658955224</v>
       </c>
       <c r="AC5">
-        <v>138733.99508064517</v>
+        <v>100012.88597014925</v>
       </c>
       <c r="AD5">
-        <v>158090.70879032259</v>
+        <v>129865.06686567164</v>
       </c>
       <c r="AE5">
-        <v>158090.70879032259</v>
+        <v>122402.13485074627</v>
       </c>
       <c r="AF5">
-        <v>154866.23653225804</v>
+        <v>116432.75567164179</v>
       </c>
       <c r="AG5">
-        <v>153252.94943548387</v>
+        <v>110461.92485074626</v>
       </c>
       <c r="AH5">
-        <v>150026.0193548387</v>
+        <v>102996.7819402985</v>
       </c>
       <c r="AI5">
-        <v>145186.12411290323</v>
+        <v>100013.23731343284</v>
       </c>
       <c r="AJ5">
-        <v>137119.4062903226</v>
+        <v>92550.170149253725</v>
       </c>
       <c r="AK5">
-        <v>132282.57903225807</v>
+        <v>89565.423432835814</v>
       </c>
       <c r="AL5">
-        <v>151638.79983870967</v>
+        <v>126879.571119403</v>
       </c>
       <c r="AM5">
-        <v>151638.79983870967</v>
+        <v>119416.63910447761</v>
       </c>
       <c r="AN5">
-        <v>145190.81725806452</v>
+        <v>111954.68910447761</v>
       </c>
       <c r="AO5">
-        <v>143577.53016129034</v>
+        <v>104489.18529850747</v>
       </c>
       <c r="AP5">
-        <v>140350.60008064515</v>
+        <v>97024.042388059694</v>
       </c>
       <c r="AQ5">
-        <v>133896.45532258064</v>
+        <v>92546.932089552225</v>
       </c>
       <c r="AR5">
-        <v>125829.41612903227</v>
+        <v>85083.864925373127</v>
       </c>
       <c r="AS5">
-        <v>122604.35467741935</v>
+        <v>82099.118208955217</v>
       </c>
       <c r="AT5">
-        <v>117766.22201612905</v>
+        <v>74638.158432835829</v>
       </c>
       <c r="AU5">
-        <v>143569.65741935483</v>
+        <v>117921.81141791045</v>
       </c>
       <c r="AV5">
-        <v>140341.49169354836</v>
+        <v>107473.01664179105</v>
       </c>
       <c r="AW5">
-        <v>133893.50911290321</v>
+        <v>100011.29895522387</v>
       </c>
       <c r="AX5">
-        <v>132280.22201612903</v>
+        <v>92545.79514925374</v>
       </c>
       <c r="AY5">
-        <v>125825.95161290323</v>
+        <v>89560.204029850749</v>
       </c>
       <c r="AZ5">
-        <v>120988.63217741936</v>
+        <v>85083.093731343281</v>
       </c>
       <c r="BA5">
-        <v>112921.59298387097</v>
+        <v>80606.226417910453</v>
       </c>
       <c r="BB5">
-        <v>108085.15766129033</v>
+        <v>77621.479701492543</v>
       </c>
       <c r="BC5">
-        <v>104859.26</v>
+        <v>70160.519925373141</v>
       </c>
       <c r="BD5">
-        <v>96796.099193548391</v>
-      </c>
-    </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.3">
+        <v>65685.236791044779</v>
+      </c>
+    </row>
+    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>59</v>
       </c>
       <c r="B6">
-        <v>-3.063504528151819E-3</v>
+        <v>3.1008265696798711E-3</v>
       </c>
       <c r="C6">
-        <v>-2.3406096226733504E-3</v>
+        <v>4.3487904855232283E-3</v>
       </c>
       <c r="D6">
-        <v>-3.5988494126451154E-3</v>
+        <v>4.5033936336737182E-3</v>
       </c>
       <c r="E6">
-        <v>-2.7239395312779087E-3</v>
+        <v>7.3598628800770668E-3</v>
       </c>
       <c r="F6">
-        <v>-4.0332684105477577E-3</v>
+        <v>7.7368784067735948E-3</v>
       </c>
       <c r="G6">
-        <v>-4.4944164109728671E-3</v>
+        <v>6.8440133387468261E-3</v>
       </c>
       <c r="H6">
-        <v>-6.3344089872676267E-3</v>
+        <v>6.8389244319484246E-3</v>
       </c>
       <c r="I6">
-        <v>-6.3344089872676267E-3</v>
+        <v>7.209157439002317E-3</v>
       </c>
       <c r="J6">
-        <v>-6.2398272812743101E-3</v>
+        <v>6.3365892353865246E-3</v>
       </c>
       <c r="K6">
-        <v>-4.5880226206733944E-3</v>
+        <v>7.7094796654113085E-3</v>
       </c>
       <c r="L6">
-        <v>-6.2052439016864877E-3</v>
+        <v>7.6183856515013573E-3</v>
       </c>
       <c r="M6">
-        <v>-6.2052439016864877E-3</v>
+        <v>9.0984823457395132E-3</v>
       </c>
       <c r="N6">
-        <v>-6.1050751785286924E-3</v>
+        <v>8.249839586959129E-3</v>
       </c>
       <c r="O6">
-        <v>-4.4002439120996171E-3</v>
+        <v>9.7503574696300825E-3</v>
       </c>
       <c r="P6">
-        <v>-5.9641224367047614E-3</v>
+        <v>8.8091094808788566E-3</v>
       </c>
       <c r="Q6">
-        <v>-5.820501630060486E-3</v>
+        <v>7.5199200503765651E-3</v>
       </c>
       <c r="R6">
-        <v>-5.820501630060486E-3</v>
+        <v>9.3719305888701841E-3</v>
       </c>
       <c r="S6">
-        <v>-5.7124046404979515E-3</v>
+        <v>8.7314279179371533E-3</v>
       </c>
       <c r="T6">
-        <v>-4.0034790756431713E-3</v>
+        <v>1.0527020238434432E-2</v>
       </c>
       <c r="U6">
-        <v>-5.5589179635850711E-3</v>
+        <v>1.0264882837396398E-2</v>
       </c>
       <c r="V6">
-        <v>-4.1346214112977968E-3</v>
+        <v>8.8034504013812312E-3</v>
       </c>
       <c r="W6">
-        <v>-5.389676014733477E-3</v>
+        <v>6.2619087487126458E-3</v>
       </c>
       <c r="X6">
-        <v>-5.389676014733477E-3</v>
+        <v>5.2901511764708109E-3</v>
       </c>
       <c r="Y6">
-        <v>-5.2727012746329426E-3</v>
+        <v>4.1957094278793376E-3</v>
       </c>
       <c r="Z6">
-        <v>-3.5591936896122861E-3</v>
+        <v>5.8956076669536995E-3</v>
       </c>
       <c r="AA6">
-        <v>-4.8641491192791455E-3</v>
+        <v>5.2899264288913984E-3</v>
       </c>
       <c r="AB6">
-        <v>-3.4169453119925162E-3</v>
+        <v>4.1640210597216438E-3</v>
       </c>
       <c r="AC6">
-        <v>-3.26571551361025E-3</v>
+        <v>2.2675211412353236E-3</v>
       </c>
       <c r="AD6">
-        <v>-4.4074696440518195E-3</v>
+        <v>7.1537431563053399E-3</v>
       </c>
       <c r="AE6">
-        <v>-4.4074696440518195E-3</v>
+        <v>6.2126585258825678E-3</v>
       </c>
       <c r="AF6">
-        <v>-4.2688245985902642E-3</v>
+        <v>5.0809069714744361E-3</v>
       </c>
       <c r="AG6">
-        <v>-2.5266932964510026E-3</v>
+        <v>6.8975561883683426E-3</v>
       </c>
       <c r="AH6">
-        <v>-3.823487168870664E-3</v>
+        <v>6.3381656627391758E-3</v>
       </c>
       <c r="AI6">
-        <v>-2.3254949607815572E-3</v>
+        <v>5.1931259029803544E-3</v>
       </c>
       <c r="AJ6">
-        <v>-1.9388940427371457E-3</v>
+        <v>5.8145904266352589E-3</v>
       </c>
       <c r="AK6">
-        <v>-2.5279519226674213E-3</v>
+        <v>9.1412359288470715E-3</v>
       </c>
       <c r="AL6">
-        <v>-4.8731242979104137E-3</v>
+        <v>9.3663200165488222E-3</v>
       </c>
       <c r="AM6">
-        <v>-4.8731242979104137E-3</v>
+        <v>8.5399824316596314E-3</v>
       </c>
       <c r="AN6">
-        <v>-3.4208212983413019E-3</v>
+        <v>7.7953203536862015E-3</v>
       </c>
       <c r="AO6">
-        <v>-1.5517625895198437E-3</v>
+        <v>6.3015899503758941E-3</v>
       </c>
       <c r="AP6">
-        <v>-2.9155386565131139E-3</v>
+        <v>5.6619093557880359E-3</v>
       </c>
       <c r="AQ6">
-        <v>1.1179384819405272E-4</v>
+        <v>4.0241060212161551E-3</v>
       </c>
       <c r="AR6">
-        <v>1.2267007568545979E-3</v>
+        <v>4.5975657900561668E-3</v>
       </c>
       <c r="AS6">
-        <v>9.6940504529991237E-4</v>
+        <v>8.1824995767945333E-3</v>
       </c>
       <c r="AT6">
-        <v>2.0868503361380205E-3</v>
+        <v>7.7312018246783109E-3</v>
       </c>
       <c r="AU6">
-        <v>-3.1929320459472914E-3</v>
+        <v>9.476448729572387E-3</v>
       </c>
       <c r="AV6">
-        <v>-4.7657911564774353E-3</v>
+        <v>8.0019341307451929E-3</v>
       </c>
       <c r="AW6">
-        <v>-3.1857807210075913E-3</v>
+        <v>7.9428892031731205E-3</v>
       </c>
       <c r="AX6">
-        <v>-1.1542296926391994E-3</v>
+        <v>6.2682912720615222E-3</v>
       </c>
       <c r="AY6">
-        <v>-9.0228636099801119E-4</v>
+        <v>4.2927399600226224E-3</v>
       </c>
       <c r="AZ6">
-        <v>4.1748451148695558E-4</v>
+        <v>2.4392154880422015E-3</v>
       </c>
       <c r="BA6">
-        <v>1.6816723443424195E-3</v>
+        <v>2.3361636154143116E-3</v>
       </c>
       <c r="BB6">
-        <v>2.4614058558695404E-3</v>
+        <v>6.0409395501085624E-3</v>
       </c>
       <c r="BC6">
-        <v>2.7839876039569785E-3</v>
+        <v>5.3331037702012019E-3</v>
       </c>
       <c r="BD6">
-        <v>7.7861765740483771E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.3">
+        <v>7.1131153588137796E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
       <c r="B7">
-        <v>-0.58002282150190121</v>
+        <v>0.61507099053578718</v>
       </c>
       <c r="C7">
-        <v>-0.4309726004734164</v>
+        <v>0.82523845256223416</v>
       </c>
       <c r="D7">
-        <v>-0.6604007254416735</v>
+        <v>0.85023370958474997</v>
       </c>
       <c r="E7">
-        <v>-0.49185028627328709</v>
+        <v>1.2839553034994831</v>
       </c>
       <c r="F7">
-        <v>-0.72573139892793537</v>
+        <v>1.3487779669281927</v>
       </c>
       <c r="G7">
-        <v>-0.80393643480564603</v>
+        <v>1.1813397041361848</v>
       </c>
       <c r="H7">
-        <v>-1.067747482760117</v>
+        <v>1.162747548647169</v>
       </c>
       <c r="I7">
-        <v>-1.067747482760117</v>
+        <v>1.2238167340738315</v>
       </c>
       <c r="J7">
-        <v>-1.0374360584737696</v>
+        <v>1.0510742084415614</v>
       </c>
       <c r="K7">
-        <v>-0.7842260759369889</v>
+        <v>1.274357571464958</v>
       </c>
       <c r="L7">
-        <v>-1.02025189938835</v>
+        <v>1.2654159852184199</v>
       </c>
       <c r="M7">
-        <v>-1.02025189938835</v>
+        <v>1.4832432562963993</v>
       </c>
       <c r="N7">
-        <v>-0.98953786023064949</v>
+        <v>1.3121294128089758</v>
       </c>
       <c r="O7">
-        <v>-0.73334724734040679</v>
+        <v>1.5435917368702785</v>
       </c>
       <c r="P7">
-        <v>-0.98967342055869578</v>
+        <v>1.350992527535704</v>
       </c>
       <c r="Q7">
-        <v>-0.94777184877788467</v>
+        <v>1.2342627214657176</v>
       </c>
       <c r="R7">
-        <v>-0.94777184877788467</v>
+        <v>1.4816405456511221</v>
       </c>
       <c r="S7">
-        <v>-0.91687059891902056</v>
+        <v>1.3413038552326912</v>
       </c>
       <c r="T7">
-        <v>-0.66026346525538393</v>
+        <v>1.5898138068024839</v>
       </c>
       <c r="U7">
-        <v>-0.91243398962343936</v>
+        <v>1.5014431094153458</v>
       </c>
       <c r="V7">
-        <v>-0.67582981166304246</v>
+        <v>1.2569591982336217</v>
       </c>
       <c r="W7">
-        <v>-0.87264556714705832</v>
+        <v>1.0352779729637323</v>
       </c>
       <c r="X7">
-        <v>-0.87264556714705832</v>
+        <v>0.87425586768672559</v>
       </c>
       <c r="Y7">
-        <v>-0.84145116695314948</v>
+        <v>0.67859225826757064</v>
       </c>
       <c r="Z7">
-        <v>-0.58342042962273921</v>
+        <v>0.94145391294181069</v>
       </c>
       <c r="AA7">
-        <v>-0.79357220660716343</v>
+        <v>0.82221365029249849</v>
       </c>
       <c r="AB7">
-        <v>-0.55502019304609707</v>
+        <v>0.62779594063586575</v>
       </c>
       <c r="AC7">
-        <v>-0.52279724885202683</v>
+        <v>0.3354736575221266</v>
       </c>
       <c r="AD7">
-        <v>-0.71271151798792742</v>
+        <v>1.1369453159638392</v>
       </c>
       <c r="AE7">
-        <v>-0.71271151798792742</v>
+        <v>0.98354308000681034</v>
       </c>
       <c r="AF7">
-        <v>-0.68032931910082795</v>
+        <v>0.77969232664032118</v>
       </c>
       <c r="AG7">
-        <v>-0.41394723535753269</v>
+        <v>1.0418945040391152</v>
       </c>
       <c r="AH7">
-        <v>-0.62342800207628513</v>
+        <v>0.92797059588895991</v>
       </c>
       <c r="AI7">
-        <v>-0.37767618059863661</v>
+        <v>0.73658900340561939</v>
       </c>
       <c r="AJ7">
-        <v>-0.31026224390726898</v>
+        <v>0.80231114543296789</v>
       </c>
       <c r="AK7">
-        <v>-0.3929176073386616</v>
+        <v>1.3244864306535722</v>
       </c>
       <c r="AL7">
-        <v>-0.78916853940796916</v>
+        <v>1.4427794453661642</v>
       </c>
       <c r="AM7">
-        <v>-0.78916853940796916</v>
+        <v>1.3069130594729137</v>
       </c>
       <c r="AN7">
-        <v>-0.5379625715179861</v>
+        <v>1.1734823036542783</v>
       </c>
       <c r="AO7">
-        <v>-0.25181573647752209</v>
+        <v>0.91871317433465893</v>
       </c>
       <c r="AP7">
-        <v>-0.47105487742045959</v>
+        <v>0.79816623558561528</v>
       </c>
       <c r="AQ7">
-        <v>1.8030146752099137E-2</v>
+        <v>0.54485741988659397</v>
       </c>
       <c r="AR7">
-        <v>0.195423982873944</v>
+        <v>0.6036615410271523</v>
       </c>
       <c r="AS7">
-        <v>0.15098866160182392</v>
+        <v>1.1315195919468835</v>
       </c>
       <c r="AT7">
-        <v>0.32023804543862328</v>
+        <v>1.0234165824173627</v>
       </c>
       <c r="AU7">
-        <v>-0.49184750146719736</v>
+        <v>1.4365146161883624</v>
       </c>
       <c r="AV7">
-        <v>-0.73330012619944229</v>
+        <v>1.1793342567685443</v>
       </c>
       <c r="AW7">
-        <v>-0.47472148340825249</v>
+        <v>1.1457187688130488</v>
       </c>
       <c r="AX7">
-        <v>-0.17777187520122792</v>
+        <v>0.87338175748077396</v>
       </c>
       <c r="AY7">
-        <v>-0.13839488589987162</v>
+        <v>0.58808065948976573</v>
       </c>
       <c r="AZ7">
-        <v>6.3198414626283131E-2</v>
+        <v>0.31998451661227761</v>
       </c>
       <c r="BA7">
-        <v>0.25078684705584919</v>
+        <v>0.30477224934067004</v>
       </c>
       <c r="BB7">
-        <v>0.35435817585475154</v>
+        <v>0.8357722662364454</v>
       </c>
       <c r="BC7">
-        <v>0.39415191833807378</v>
+        <v>0.70704321315377761</v>
       </c>
       <c r="BD7">
-        <v>1.1952336126952594</v>
-      </c>
-    </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.3">
+        <v>8.9573343578339515E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>61</v>
       </c>
       <c r="B8">
-        <v>-993.6500000000708</v>
+        <v>-576.44000000002984</v>
       </c>
       <c r="C8">
-        <v>-993.65000000007103</v>
+        <v>-478.09000000003061</v>
       </c>
       <c r="D8">
-        <v>-993.65000000007092</v>
+        <v>-532.30500000002189</v>
       </c>
       <c r="E8">
-        <v>-903.95000000004438</v>
+        <v>-419.65499999999889</v>
       </c>
       <c r="F8">
-        <v>-903.95000000004461</v>
+        <v>-412.57000000000346</v>
       </c>
       <c r="G8">
-        <v>-939.47000000004732</v>
+        <v>-515.09000000000231</v>
       </c>
       <c r="H8">
-        <v>-901.45000000003893</v>
+        <v>-413.07499999999658</v>
       </c>
       <c r="I8">
-        <v>-901.45000000003893</v>
+        <v>-405.99000000000115</v>
       </c>
       <c r="J8">
-        <v>-883.75000000004809</v>
+        <v>-509.91000000000281</v>
       </c>
       <c r="K8">
-        <v>-883.75000000004809</v>
+        <v>-501.74000000000245</v>
       </c>
       <c r="L8">
-        <v>-850.31000000003053</v>
+        <v>-413.07499999999658</v>
       </c>
       <c r="M8">
-        <v>-850.31000000003053</v>
+        <v>-405.99000000000115</v>
       </c>
       <c r="N8">
-        <v>-832.61000000003958</v>
+        <v>-509.91000000000281</v>
       </c>
       <c r="O8">
-        <v>-832.61000000003958</v>
+        <v>-501.74000000000262</v>
       </c>
       <c r="P8">
-        <v>-943.20000000003267</v>
+        <v>-501.74000000000251</v>
       </c>
       <c r="Q8">
-        <v>-819.83000000003074</v>
+        <v>-413.07499999999658</v>
       </c>
       <c r="R8">
-        <v>-819.83000000003074</v>
+        <v>-405.9900000000012</v>
       </c>
       <c r="S8">
-        <v>-802.1300000000399</v>
+        <v>-509.91000000000281</v>
       </c>
       <c r="T8">
-        <v>-802.13000000003967</v>
+        <v>-501.74000000000262</v>
       </c>
       <c r="U8">
-        <v>-912.720000000033</v>
+        <v>-501.74000000000245</v>
       </c>
       <c r="V8">
-        <v>-795.6600000000301</v>
+        <v>-501.74000000000251</v>
       </c>
       <c r="W8">
-        <v>-785.70000000002938</v>
+        <v>-297.59000000001583</v>
       </c>
       <c r="X8">
-        <v>-785.70000000002938</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="Y8">
-        <v>-768.00000000003865</v>
+        <v>-393.24000000000194</v>
       </c>
       <c r="Z8">
-        <v>-768.00000000003854</v>
+        <v>-385.07000000000158</v>
       </c>
       <c r="AA8">
-        <v>-860.46000000003164</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AB8">
-        <v>-743.40000000002897</v>
+        <v>-385.07000000000158</v>
       </c>
       <c r="AC8">
-        <v>-760.97500000002151</v>
+        <v>-399.46500000001203</v>
       </c>
       <c r="AD8">
-        <v>-704.36000000001422</v>
+        <v>-297.59000000001589</v>
       </c>
       <c r="AE8">
-        <v>-704.36000000001422</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="AF8">
-        <v>-686.66000000002327</v>
+        <v>-393.24000000000188</v>
       </c>
       <c r="AG8">
-        <v>-686.66000000002327</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AH8">
-        <v>-779.12000000001638</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AI8">
-        <v>-662.06000000001359</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AJ8">
-        <v>-668.1150000000066</v>
+        <v>-291.24500000001399</v>
       </c>
       <c r="AK8">
-        <v>-690.14500000002704</v>
+        <v>-291.24500000001399</v>
       </c>
       <c r="AL8">
-        <v>-730.14999999999793</v>
+        <v>-297.59000000001595</v>
       </c>
       <c r="AM8">
-        <v>-730.14999999999793</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="AN8">
-        <v>-609.96999999998661</v>
+        <v>-393.24000000000194</v>
       </c>
       <c r="AO8">
-        <v>-609.96999999998673</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AP8">
-        <v>-702.42999999997983</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AQ8">
-        <v>-568.31000000000154</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AR8">
-        <v>-570.93499999999472</v>
+        <v>-291.24500000001387</v>
       </c>
       <c r="AS8">
-        <v>-570.93499999999483</v>
+        <v>-291.24500000001399</v>
       </c>
       <c r="AT8">
-        <v>-562.22999999999297</v>
+        <v>-291.24500000001399</v>
       </c>
       <c r="AU8">
-        <v>-697.46999999998388</v>
+        <v>-297.59000000001589</v>
       </c>
       <c r="AV8">
-        <v>-697.46999999998411</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="AW8">
-        <v>-577.28999999997268</v>
+        <v>-393.24000000000194</v>
       </c>
       <c r="AX8">
-        <v>-577.28999999997257</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AY8">
-        <v>-576.55999999998403</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="AZ8">
-        <v>-529.65499999999747</v>
+        <v>-385.07000000000153</v>
       </c>
       <c r="BA8">
-        <v>-532.27999999999076</v>
+        <v>-291.24500000001382</v>
       </c>
       <c r="BB8">
-        <v>-532.27999999999065</v>
+        <v>-291.24500000001382</v>
       </c>
       <c r="BC8">
-        <v>-532.27999999999065</v>
+        <v>-291.24500000001387</v>
       </c>
       <c r="BD8">
-        <v>-361.18499999999784</v>
-      </c>
-    </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.3">
+        <v>-291.24500000001387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -1999,330 +1989,330 @@
         <v>43</v>
       </c>
       <c r="C9">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
         <v>49</v>
       </c>
       <c r="E9">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F9">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H9">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="I9">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="J9">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K9">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L9">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="M9">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N9">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="O9">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="P9">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q9">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="R9">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="S9">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="T9">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="U9">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="V9">
         <v>55</v>
       </c>
       <c r="W9">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="X9">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="Y9">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="Z9">
         <v>63</v>
       </c>
       <c r="AA9">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AB9">
+        <v>58</v>
+      </c>
+      <c r="AC9">
+        <v>57</v>
+      </c>
+      <c r="AD9">
+        <v>79</v>
+      </c>
+      <c r="AE9">
+        <v>75</v>
+      </c>
+      <c r="AF9">
+        <v>71</v>
+      </c>
+      <c r="AG9">
+        <v>68</v>
+      </c>
+      <c r="AH9">
+        <v>65</v>
+      </c>
+      <c r="AI9">
         <v>63</v>
       </c>
-      <c r="AC9">
-        <v>61</v>
-      </c>
-      <c r="AD9">
-        <v>65</v>
-      </c>
-      <c r="AE9">
-        <v>65</v>
-      </c>
-      <c r="AF9">
-        <v>65</v>
-      </c>
-      <c r="AG9">
-        <v>65</v>
-      </c>
-      <c r="AH9">
+      <c r="AJ9">
+        <v>60</v>
+      </c>
+      <c r="AK9">
+        <v>59</v>
+      </c>
+      <c r="AL9">
+        <v>85</v>
+      </c>
+      <c r="AM9">
+        <v>81</v>
+      </c>
+      <c r="AN9">
+        <v>75</v>
+      </c>
+      <c r="AO9">
+        <v>69</v>
+      </c>
+      <c r="AP9">
         <v>66</v>
       </c>
-      <c r="AI9">
-        <v>65</v>
-      </c>
-      <c r="AJ9">
-        <v>64</v>
-      </c>
-      <c r="AK9">
-        <v>63</v>
-      </c>
-      <c r="AL9">
-        <v>68</v>
-      </c>
-      <c r="AM9">
-        <v>68</v>
-      </c>
-      <c r="AN9">
-        <v>66</v>
-      </c>
-      <c r="AO9">
-        <v>66</v>
-      </c>
-      <c r="AP9">
-        <v>67</v>
-      </c>
       <c r="AQ9">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AR9">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AS9">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="AT9">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AU9">
+        <v>81</v>
+      </c>
+      <c r="AV9">
         <v>74</v>
-      </c>
-      <c r="AV9">
-        <v>71</v>
       </c>
       <c r="AW9">
         <v>69</v>
       </c>
       <c r="AX9">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="AY9">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="AZ9">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="BA9">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="BB9">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="BC9">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="BD9">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>63</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AP10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AQ10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AR10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC10">
         <v>3</v>
@@ -2337,16 +2327,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B97D23D-E068-42FB-BD20-7E3DCD282169}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBAF76C-FF2D-469D-B11C-F23BDFF80633}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2381,219 +2372,219 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1E-4</v>
       </c>
       <c r="B2" s="2">
-        <v>-277.00500000000022</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>287.63000000009271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="B3" s="2">
-        <v>-207.8950000000201</v>
+        <v>386.00000000009095</v>
       </c>
       <c r="C3">
-        <v>-316.77500000002817</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>392.52000000009639</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="B4" s="2">
-        <v>-233.22500000000616</v>
+        <v>594.42000000005623</v>
       </c>
       <c r="C4">
-        <v>-342.10500000001423</v>
+        <v>612.50000000004343</v>
       </c>
       <c r="D4">
-        <v>-377.62500000001683</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>530.87000000005389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="B5" s="2">
-        <v>-517.01500000000908</v>
+        <v>546.88000000004979</v>
       </c>
       <c r="C5">
-        <v>-517.01500000000908</v>
+        <v>564.96000000003687</v>
       </c>
       <c r="D5">
-        <v>-499.31500000001824</v>
+        <v>481.38000000003279</v>
       </c>
       <c r="E5">
-        <v>-363.46500000000839</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>567.18000000003485</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="B6" s="2">
-        <v>-491.57500000000789</v>
+        <v>590.9400000000503</v>
       </c>
       <c r="C6">
-        <v>-491.57500000000789</v>
+        <v>683.92000000003361</v>
       </c>
       <c r="D6">
-        <v>-473.87500000001694</v>
+        <v>600.34000000002959</v>
       </c>
       <c r="E6">
-        <v>-338.02500000000714</v>
+        <v>686.14000000003159</v>
       </c>
       <c r="F6">
-        <v>-448.61500000000012</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>584.68000000000882</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="B7" s="2">
-        <v>-461.09500000000799</v>
+        <v>571.28000000006477</v>
       </c>
       <c r="C7">
-        <v>-461.09500000000799</v>
+        <v>674.50000000004411</v>
       </c>
       <c r="D7">
-        <v>-443.39500000001715</v>
+        <v>607.46000000002664</v>
       </c>
       <c r="E7">
-        <v>-307.54500000000735</v>
+        <v>698.71000000001902</v>
       </c>
       <c r="F7">
-        <v>-418.13500000000045</v>
+        <v>640.25999999999624</v>
       </c>
       <c r="G7">
-        <v>-301.07499999999777</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>535.02999999999281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="B8" s="2">
-        <v>-426.96500000000674</v>
+        <v>445.66000000003567</v>
       </c>
       <c r="C8">
-        <v>-426.96500000000674</v>
+        <v>355.35000000000866</v>
       </c>
       <c r="D8">
-        <v>-409.2650000000159</v>
+        <v>271.77000000000453</v>
       </c>
       <c r="E8">
-        <v>-273.4150000000061</v>
+        <v>363.01999999999703</v>
       </c>
       <c r="F8">
-        <v>-365.8749999999992</v>
+        <v>304.5699999999743</v>
       </c>
       <c r="G8">
-        <v>-248.81499999999653</v>
+        <v>233.0899999999786</v>
       </c>
       <c r="H8">
-        <v>-224.73499999999558</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>121.48999999996664</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="B9" s="2">
-        <v>-345.62499999999159</v>
+        <v>497.69000000005383</v>
       </c>
       <c r="C9">
-        <v>-345.62499999999159</v>
+        <v>407.38000000002671</v>
       </c>
       <c r="D9">
-        <v>-327.92500000000064</v>
+        <v>316.92000000001309</v>
       </c>
       <c r="E9">
-        <v>-192.07499999999084</v>
+        <v>408.17000000000553</v>
       </c>
       <c r="F9">
-        <v>-284.53499999998394</v>
+        <v>349.71999999998275</v>
       </c>
       <c r="G9">
-        <v>-167.47499999998126</v>
+        <v>278.23999999998716</v>
       </c>
       <c r="H9">
-        <v>-131.87499999998056</v>
+        <v>288.28999999999019</v>
       </c>
       <c r="I9">
-        <v>-165.87500000000097</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>438.60999999998575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="B10" s="2">
-        <v>-366.54499999999496</v>
+        <v>636.64000000006831</v>
       </c>
       <c r="C10">
-        <v>-366.54499999999496</v>
+        <v>546.33000000004131</v>
       </c>
       <c r="D10">
-        <v>-246.36499999998364</v>
+        <v>467.53000000004209</v>
       </c>
       <c r="E10">
-        <v>-110.5149999999739</v>
+        <v>352.74000000002104</v>
       </c>
       <c r="F10">
-        <v>-202.974999999967</v>
+        <v>294.28999999999826</v>
       </c>
       <c r="G10">
-        <v>7.4250000000269551</v>
+        <v>199.5099999999909</v>
       </c>
       <c r="H10">
-        <v>76.565000000027794</v>
+        <v>209.55999999999392</v>
       </c>
       <c r="I10">
-        <v>58.955000000014991</v>
+        <v>359.87999999998954</v>
       </c>
       <c r="J10">
-        <v>121.90500000003158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>309.12999999994781</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1E-3</v>
       </c>
       <c r="B11" s="2">
-        <v>-227.38499999996645</v>
+        <v>598.6500000000708</v>
       </c>
       <c r="C11">
-        <v>-331.76499999998231</v>
+        <v>460.71000000005023</v>
       </c>
       <c r="D11">
-        <v>-211.58499999997088</v>
+        <v>425.56000000005366</v>
       </c>
       <c r="E11">
-        <v>-75.734999999961133</v>
+        <v>310.77000000003255</v>
       </c>
       <c r="F11">
-        <v>-56.314999999959468</v>
+        <v>205.96000000002829</v>
       </c>
       <c r="G11">
-        <v>25.05500000003218</v>
+        <v>111.18000000002084</v>
       </c>
       <c r="H11">
-        <v>94.195000000033133</v>
+        <v>100.88000000001978</v>
       </c>
       <c r="I11">
-        <v>131.96500000004096</v>
+        <v>251.20000000001534</v>
       </c>
       <c r="J11">
-        <v>144.80500000005048</v>
+        <v>200.44999999997356</v>
       </c>
       <c r="K11">
-        <v>373.84500000003447</v>
+        <v>25.029999999948245</v>
       </c>
     </row>
   </sheetData>
@@ -2602,17 +2593,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B74944-60C4-474C-A8F8-73654F361D11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32CE67A-5E0B-4C6F-94F9-1D4918A80036}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2647,219 +2636,219 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1E-4</v>
       </c>
       <c r="B2" s="2">
-        <v>182288.64193548387</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>173150.39111940298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="B3" s="2">
-        <v>179062.8885483871</v>
+        <v>165685.91559701491</v>
       </c>
       <c r="C3">
-        <v>177450.7145967742</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>162700.41208955224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="B4" s="2">
-        <v>172610.88016129032</v>
+        <v>150761.50440298507</v>
       </c>
       <c r="C4">
-        <v>170998.70620967742</v>
+        <v>147777.08440298509</v>
       </c>
       <c r="D4">
-        <v>169386.1739516129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>144791.84716417914</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="B5" s="2">
-        <v>164546.09137096777</v>
+        <v>149269.47604477612</v>
       </c>
       <c r="C5">
-        <v>164546.09137096777</v>
+        <v>146285.05604477614</v>
       </c>
       <c r="D5">
-        <v>161321.61911290322</v>
+        <v>141807.51925373133</v>
       </c>
       <c r="E5">
-        <v>159708.33201612905</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>137329.11246268658</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="B6" s="2">
-        <v>159706.08338709676</v>
+        <v>144792.88007462685</v>
       </c>
       <c r="C6">
-        <v>159706.08338709676</v>
+        <v>140314.68305970149</v>
       </c>
       <c r="D6">
-        <v>156481.61112903227</v>
+        <v>135837.14626865674</v>
       </c>
       <c r="E6">
-        <v>154868.32403225807</v>
+        <v>131358.73947761193</v>
       </c>
       <c r="F6">
-        <v>151641.3939516129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>123894.77835820896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="B7" s="2">
-        <v>159705.74</v>
+        <v>141808.59985074628</v>
       </c>
       <c r="C7">
-        <v>159705.74</v>
+        <v>134344.42932835821</v>
       </c>
       <c r="D7">
-        <v>156481.26774193547</v>
+        <v>129867.11268656717</v>
       </c>
       <c r="E7">
-        <v>154867.9806451613</v>
+        <v>123896.28186567164</v>
       </c>
       <c r="F7">
-        <v>151641.05056451613</v>
+        <v>116431.13895522388</v>
       </c>
       <c r="G7">
-        <v>146801.15532258066</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>113446.7306716418</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="B8" s="2">
-        <v>159705.59967741935</v>
+        <v>132850.65305970149</v>
       </c>
       <c r="C8">
-        <v>159705.59967741935</v>
+        <v>125387.7210447761</v>
       </c>
       <c r="D8">
-        <v>156481.12741935483</v>
+        <v>120910.18425373134</v>
       </c>
       <c r="E8">
-        <v>154867.84032258068</v>
+        <v>114939.35343283582</v>
       </c>
       <c r="F8">
-        <v>151640.91024193549</v>
+        <v>107474.21052238806</v>
       </c>
       <c r="G8">
-        <v>146801.01499999998</v>
+        <v>104490.6658955224</v>
       </c>
       <c r="H8">
-        <v>138733.99508064517</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>100012.88597014925</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="B9" s="2">
-        <v>158090.70879032259</v>
+        <v>129865.06686567164</v>
       </c>
       <c r="C9">
-        <v>158090.70879032259</v>
+        <v>122402.13485074627</v>
       </c>
       <c r="D9">
-        <v>154866.23653225804</v>
+        <v>116432.75567164179</v>
       </c>
       <c r="E9">
-        <v>153252.94943548387</v>
+        <v>110461.92485074626</v>
       </c>
       <c r="F9">
-        <v>150026.0193548387</v>
+        <v>102996.7819402985</v>
       </c>
       <c r="G9">
-        <v>145186.12411290323</v>
+        <v>100013.23731343284</v>
       </c>
       <c r="H9">
-        <v>137119.4062903226</v>
+        <v>92550.170149253725</v>
       </c>
       <c r="I9">
-        <v>132282.57903225807</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>89565.423432835814</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="B10" s="2">
-        <v>151638.79983870967</v>
+        <v>126879.571119403</v>
       </c>
       <c r="C10">
-        <v>151638.79983870967</v>
+        <v>119416.63910447761</v>
       </c>
       <c r="D10">
-        <v>145190.81725806452</v>
+        <v>111954.68910447761</v>
       </c>
       <c r="E10">
-        <v>143577.53016129034</v>
+        <v>104489.18529850747</v>
       </c>
       <c r="F10">
-        <v>140350.60008064515</v>
+        <v>97024.042388059694</v>
       </c>
       <c r="G10">
-        <v>133896.45532258064</v>
+        <v>92546.932089552225</v>
       </c>
       <c r="H10">
-        <v>125829.41612903227</v>
+        <v>85083.864925373127</v>
       </c>
       <c r="I10">
-        <v>122604.35467741935</v>
+        <v>82099.118208955217</v>
       </c>
       <c r="J10">
-        <v>117766.22201612905</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>74638.158432835829</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1E-3</v>
       </c>
       <c r="B11" s="2">
-        <v>143569.65741935483</v>
+        <v>117921.81141791045</v>
       </c>
       <c r="C11">
-        <v>140341.49169354836</v>
+        <v>107473.01664179105</v>
       </c>
       <c r="D11">
-        <v>133893.50911290321</v>
+        <v>100011.29895522387</v>
       </c>
       <c r="E11">
-        <v>132280.22201612903</v>
+        <v>92545.79514925374</v>
       </c>
       <c r="F11">
-        <v>125825.95161290323</v>
+        <v>89560.204029850749</v>
       </c>
       <c r="G11">
-        <v>120988.63217741936</v>
+        <v>85083.093731343281</v>
       </c>
       <c r="H11">
-        <v>112921.59298387097</v>
+        <v>80606.226417910453</v>
       </c>
       <c r="I11">
-        <v>108085.15766129033</v>
+        <v>77621.479701492543</v>
       </c>
       <c r="J11">
-        <v>104859.26</v>
+        <v>70160.519925373141</v>
       </c>
       <c r="K11">
-        <v>96796.099193548391</v>
+        <v>65685.236791044779</v>
       </c>
     </row>
   </sheetData>
@@ -2868,16 +2857,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49341E58-2666-4241-940A-E9D9BB592716}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24F3A96C-F9B8-44F4-858E-7E8AABD330DA}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2912,288 +2900,220 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1E-4</v>
       </c>
-      <c r="B2" s="4">
-        <v>-3.063504528151819E-3</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="1">
+        <v>3.1008265696798711E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="B3" s="4">
-        <v>-2.3406096226733504E-3</v>
-      </c>
-      <c r="C3" s="4">
-        <v>-3.5988494126451154E-3</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>4.3487904855232283E-3</v>
+      </c>
+      <c r="C3">
+        <v>4.5033936336737182E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="B4" s="4">
-        <v>-2.7239395312779087E-3</v>
-      </c>
-      <c r="C4" s="4">
-        <v>-4.0332684105477577E-3</v>
-      </c>
-      <c r="D4" s="4">
-        <v>-4.4944164109728671E-3</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>7.3598628800770668E-3</v>
+      </c>
+      <c r="C4">
+        <v>7.7368784067735948E-3</v>
+      </c>
+      <c r="D4">
+        <v>6.8440133387468261E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="B5" s="4">
-        <v>-6.3344089872676267E-3</v>
-      </c>
-      <c r="C5" s="4">
-        <v>-6.3344089872676267E-3</v>
-      </c>
-      <c r="D5" s="4">
-        <v>-6.2398272812743101E-3</v>
-      </c>
-      <c r="E5" s="4">
-        <v>-4.5880226206733944E-3</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>6.8389244319484246E-3</v>
+      </c>
+      <c r="C5">
+        <v>7.209157439002317E-3</v>
+      </c>
+      <c r="D5">
+        <v>6.3365892353865246E-3</v>
+      </c>
+      <c r="E5">
+        <v>7.7094796654113085E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="B6" s="4">
-        <v>-6.2052439016864877E-3</v>
-      </c>
-      <c r="C6" s="4">
-        <v>-6.2052439016864877E-3</v>
-      </c>
-      <c r="D6" s="4">
-        <v>-6.1050751785286924E-3</v>
-      </c>
-      <c r="E6" s="4">
-        <v>-4.4002439120996171E-3</v>
-      </c>
-      <c r="F6" s="4">
-        <v>-5.9641224367047614E-3</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>7.6183856515013573E-3</v>
+      </c>
+      <c r="C6">
+        <v>9.0984823457395132E-3</v>
+      </c>
+      <c r="D6">
+        <v>8.249839586959129E-3</v>
+      </c>
+      <c r="E6">
+        <v>9.7503574696300825E-3</v>
+      </c>
+      <c r="F6">
+        <v>8.8091094808788566E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="B7" s="4">
-        <v>-5.820501630060486E-3</v>
-      </c>
-      <c r="C7" s="4">
-        <v>-5.820501630060486E-3</v>
-      </c>
-      <c r="D7" s="4">
-        <v>-5.7124046404979515E-3</v>
-      </c>
-      <c r="E7" s="4">
-        <v>-4.0034790756431713E-3</v>
-      </c>
-      <c r="F7" s="4">
-        <v>-5.5589179635850711E-3</v>
-      </c>
-      <c r="G7" s="4">
-        <v>-4.1346214112977968E-3</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>7.5199200503765651E-3</v>
+      </c>
+      <c r="C7">
+        <v>9.3719305888701841E-3</v>
+      </c>
+      <c r="D7">
+        <v>8.7314279179371533E-3</v>
+      </c>
+      <c r="E7">
+        <v>1.0527020238434432E-2</v>
+      </c>
+      <c r="F7">
+        <v>1.0264882837396398E-2</v>
+      </c>
+      <c r="G7">
+        <v>8.8034504013812312E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="B8" s="4">
-        <v>-5.389676014733477E-3</v>
-      </c>
-      <c r="C8" s="4">
-        <v>-5.389676014733477E-3</v>
-      </c>
-      <c r="D8" s="4">
-        <v>-5.2727012746329426E-3</v>
-      </c>
-      <c r="E8" s="4">
-        <v>-3.5591936896122861E-3</v>
-      </c>
-      <c r="F8" s="4">
-        <v>-4.8641491192791455E-3</v>
-      </c>
-      <c r="G8" s="4">
-        <v>-3.4169453119925162E-3</v>
-      </c>
-      <c r="H8" s="4">
-        <v>-3.26571551361025E-3</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>6.2619087487126458E-3</v>
+      </c>
+      <c r="C8">
+        <v>5.2901511764708109E-3</v>
+      </c>
+      <c r="D8">
+        <v>4.1957094278793376E-3</v>
+      </c>
+      <c r="E8">
+        <v>5.8956076669536995E-3</v>
+      </c>
+      <c r="F8">
+        <v>5.2899264288913984E-3</v>
+      </c>
+      <c r="G8">
+        <v>4.1640210597216438E-3</v>
+      </c>
+      <c r="H8">
+        <v>2.2675211412353236E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="B9" s="4">
-        <v>-4.4074696440518195E-3</v>
-      </c>
-      <c r="C9" s="4">
-        <v>-4.4074696440518195E-3</v>
-      </c>
-      <c r="D9" s="4">
-        <v>-4.2688245985902642E-3</v>
-      </c>
-      <c r="E9" s="4">
-        <v>-2.5266932964510026E-3</v>
-      </c>
-      <c r="F9" s="4">
-        <v>-3.823487168870664E-3</v>
-      </c>
-      <c r="G9" s="4">
-        <v>-2.3254949607815572E-3</v>
-      </c>
-      <c r="H9" s="4">
-        <v>-1.9388940427371457E-3</v>
-      </c>
-      <c r="I9" s="4">
-        <v>-2.5279519226674213E-3</v>
-      </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>7.1537431563053399E-3</v>
+      </c>
+      <c r="C9">
+        <v>6.2126585258825678E-3</v>
+      </c>
+      <c r="D9">
+        <v>5.0809069714744361E-3</v>
+      </c>
+      <c r="E9">
+        <v>6.8975561883683426E-3</v>
+      </c>
+      <c r="F9">
+        <v>6.3381656627391758E-3</v>
+      </c>
+      <c r="G9">
+        <v>5.1931259029803544E-3</v>
+      </c>
+      <c r="H9">
+        <v>5.8145904266352589E-3</v>
+      </c>
+      <c r="I9">
+        <v>9.1412359288470715E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="B10" s="4">
-        <v>-4.8731242979104137E-3</v>
-      </c>
-      <c r="C10" s="4">
-        <v>-4.8731242979104137E-3</v>
-      </c>
-      <c r="D10" s="4">
-        <v>-3.4208212983413019E-3</v>
-      </c>
-      <c r="E10" s="4">
-        <v>-1.5517625895198437E-3</v>
-      </c>
-      <c r="F10" s="4">
-        <v>-2.9155386565131139E-3</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1.1179384819405272E-4</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1.2267007568545979E-3</v>
-      </c>
-      <c r="I10" s="4">
-        <v>9.6940504529991237E-4</v>
-      </c>
-      <c r="J10" s="4">
-        <v>2.0868503361380205E-3</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>9.3663200165488222E-3</v>
+      </c>
+      <c r="C10">
+        <v>8.5399824316596314E-3</v>
+      </c>
+      <c r="D10">
+        <v>7.7953203536862015E-3</v>
+      </c>
+      <c r="E10">
+        <v>6.3015899503758941E-3</v>
+      </c>
+      <c r="F10">
+        <v>5.6619093557880359E-3</v>
+      </c>
+      <c r="G10">
+        <v>4.0241060212161551E-3</v>
+      </c>
+      <c r="H10">
+        <v>4.5975657900561668E-3</v>
+      </c>
+      <c r="I10">
+        <v>8.1824995767945333E-3</v>
+      </c>
+      <c r="J10">
+        <v>7.7312018246783109E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1E-3</v>
       </c>
-      <c r="B11" s="4">
-        <v>-3.1929320459472914E-3</v>
-      </c>
-      <c r="C11" s="4">
-        <v>-4.7657911564774353E-3</v>
-      </c>
-      <c r="D11" s="4">
-        <v>-3.1857807210075913E-3</v>
-      </c>
-      <c r="E11" s="4">
-        <v>-1.1542296926391994E-3</v>
-      </c>
-      <c r="F11" s="4">
-        <v>-9.0228636099801119E-4</v>
-      </c>
-      <c r="G11" s="4">
-        <v>4.1748451148695558E-4</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1.6816723443424195E-3</v>
-      </c>
-      <c r="I11" s="4">
-        <v>2.4614058558695404E-3</v>
-      </c>
-      <c r="J11" s="4">
-        <v>2.7839876039569785E-3</v>
-      </c>
-      <c r="K11" s="4">
-        <v>7.7861765740483771E-3</v>
-      </c>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="B11" s="1">
+        <v>9.476448729572387E-3</v>
+      </c>
+      <c r="C11">
+        <v>8.0019341307451929E-3</v>
+      </c>
+      <c r="D11">
+        <v>7.9428892031731205E-3</v>
+      </c>
+      <c r="E11">
+        <v>6.2682912720615222E-3</v>
+      </c>
+      <c r="F11">
+        <v>4.2927399600226224E-3</v>
+      </c>
+      <c r="G11">
+        <v>2.4392154880422015E-3</v>
+      </c>
+      <c r="H11">
+        <v>2.3361636154143116E-3</v>
+      </c>
+      <c r="I11">
+        <v>6.0409395501085624E-3</v>
+      </c>
+      <c r="J11">
+        <v>5.3331037702012019E-3</v>
+      </c>
+      <c r="K11">
+        <v>7.1131153588137796E-4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3201,16 +3121,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFD4813-4D3C-429E-87EB-5B4B716E9015}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986E81BB-474B-4F08-8876-48B659AEE1FB}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -3245,219 +3164,219 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1E-4</v>
       </c>
       <c r="B2" s="3">
-        <v>-0.58002282150190121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.61507099053578718</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="B3" s="3">
-        <v>-0.4309726004734164</v>
+        <v>0.82523845256223416</v>
       </c>
       <c r="C3">
-        <v>-0.6604007254416735</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.85023370958474997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="B4" s="3">
-        <v>-0.49185028627328709</v>
+        <v>1.2839553034994831</v>
       </c>
       <c r="C4">
-        <v>-0.72573139892793537</v>
+        <v>1.3487779669281927</v>
       </c>
       <c r="D4">
-        <v>-0.80393643480564603</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.1813397041361848</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="B5" s="3">
-        <v>-1.067747482760117</v>
+        <v>1.162747548647169</v>
       </c>
       <c r="C5">
-        <v>-1.067747482760117</v>
+        <v>1.2238167340738315</v>
       </c>
       <c r="D5">
-        <v>-1.0374360584737696</v>
+        <v>1.0510742084415614</v>
       </c>
       <c r="E5">
-        <v>-0.7842260759369889</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.274357571464958</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="B6" s="3">
-        <v>-1.02025189938835</v>
+        <v>1.2654159852184199</v>
       </c>
       <c r="C6">
-        <v>-1.02025189938835</v>
+        <v>1.4832432562963993</v>
       </c>
       <c r="D6">
-        <v>-0.98953786023064949</v>
+        <v>1.3121294128089758</v>
       </c>
       <c r="E6">
-        <v>-0.73334724734040679</v>
+        <v>1.5435917368702785</v>
       </c>
       <c r="F6">
-        <v>-0.98967342055869578</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.350992527535704</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="B7" s="3">
-        <v>-0.94777184877788467</v>
+        <v>1.2342627214657176</v>
       </c>
       <c r="C7">
-        <v>-0.94777184877788467</v>
+        <v>1.4816405456511221</v>
       </c>
       <c r="D7">
-        <v>-0.91687059891902056</v>
+        <v>1.3413038552326912</v>
       </c>
       <c r="E7">
-        <v>-0.66026346525538393</v>
+        <v>1.5898138068024839</v>
       </c>
       <c r="F7">
-        <v>-0.91243398962343936</v>
+        <v>1.5014431094153458</v>
       </c>
       <c r="G7">
-        <v>-0.67582981166304246</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.2569591982336217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="B8" s="3">
-        <v>-0.87264556714705832</v>
+        <v>1.0352779729637323</v>
       </c>
       <c r="C8">
-        <v>-0.87264556714705832</v>
+        <v>0.87425586768672559</v>
       </c>
       <c r="D8">
-        <v>-0.84145116695314948</v>
+        <v>0.67859225826757064</v>
       </c>
       <c r="E8">
-        <v>-0.58342042962273921</v>
+        <v>0.94145391294181069</v>
       </c>
       <c r="F8">
-        <v>-0.79357220660716343</v>
+        <v>0.82221365029249849</v>
       </c>
       <c r="G8">
-        <v>-0.55502019304609707</v>
+        <v>0.62779594063586575</v>
       </c>
       <c r="H8">
-        <v>-0.52279724885202683</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.3354736575221266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="B9" s="3">
-        <v>-0.71271151798792742</v>
+        <v>1.1369453159638392</v>
       </c>
       <c r="C9">
-        <v>-0.71271151798792742</v>
+        <v>0.98354308000681034</v>
       </c>
       <c r="D9">
-        <v>-0.68032931910082795</v>
+        <v>0.77969232664032118</v>
       </c>
       <c r="E9">
-        <v>-0.41394723535753269</v>
+        <v>1.0418945040391152</v>
       </c>
       <c r="F9">
-        <v>-0.62342800207628513</v>
+        <v>0.92797059588895991</v>
       </c>
       <c r="G9">
-        <v>-0.37767618059863661</v>
+        <v>0.73658900340561939</v>
       </c>
       <c r="H9">
-        <v>-0.31026224390726898</v>
+        <v>0.80231114543296789</v>
       </c>
       <c r="I9">
-        <v>-0.3929176073386616</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.3244864306535722</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="B10" s="3">
-        <v>-0.78916853940796916</v>
+        <v>1.4427794453661642</v>
       </c>
       <c r="C10">
-        <v>-0.78916853940796916</v>
+        <v>1.3069130594729137</v>
       </c>
       <c r="D10">
-        <v>-0.5379625715179861</v>
+        <v>1.1734823036542783</v>
       </c>
       <c r="E10">
-        <v>-0.25181573647752209</v>
+        <v>0.91871317433465893</v>
       </c>
       <c r="F10">
-        <v>-0.47105487742045959</v>
+        <v>0.79816623558561528</v>
       </c>
       <c r="G10">
-        <v>1.8030146752099137E-2</v>
+        <v>0.54485741988659397</v>
       </c>
       <c r="H10">
-        <v>0.195423982873944</v>
+        <v>0.6036615410271523</v>
       </c>
       <c r="I10">
-        <v>0.15098866160182392</v>
+        <v>1.1315195919468835</v>
       </c>
       <c r="J10">
-        <v>0.32023804543862328</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.0234165824173627</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1E-3</v>
       </c>
       <c r="B11" s="3">
-        <v>-0.49184750146719736</v>
+        <v>1.4365146161883624</v>
       </c>
       <c r="C11">
-        <v>-0.73330012619944229</v>
+        <v>1.1793342567685443</v>
       </c>
       <c r="D11">
-        <v>-0.47472148340825249</v>
+        <v>1.1457187688130488</v>
       </c>
       <c r="E11">
-        <v>-0.17777187520122792</v>
+        <v>0.87338175748077396</v>
       </c>
       <c r="F11">
-        <v>-0.13839488589987162</v>
+        <v>0.58808065948976573</v>
       </c>
       <c r="G11">
-        <v>6.3198414626283131E-2</v>
+        <v>0.31998451661227761</v>
       </c>
       <c r="H11">
-        <v>0.25078684705584919</v>
+        <v>0.30477224934067004</v>
       </c>
       <c r="I11">
-        <v>0.35435817585475154</v>
+        <v>0.8357722662364454</v>
       </c>
       <c r="J11">
-        <v>0.39415191833807378</v>
+        <v>0.70704321315377761</v>
       </c>
       <c r="K11">
-        <v>1.1952336126952594</v>
+        <v>8.9573343578339515E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3466,19 +3385,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7538D399-920B-4008-8D4A-0F195903D600}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C824A34-33C5-4226-8DD6-B5C7FA007C70}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -3513,219 +3430,219 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1E-4</v>
       </c>
       <c r="B2" s="2">
-        <v>-993.6500000000708</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-576.44000000002984</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="B3" s="2">
-        <v>-993.65000000007103</v>
+        <v>-478.09000000003061</v>
       </c>
       <c r="C3">
-        <v>-993.65000000007092</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-532.30500000002189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="B4" s="2">
-        <v>-903.95000000004438</v>
+        <v>-419.65499999999889</v>
       </c>
       <c r="C4">
-        <v>-903.95000000004461</v>
+        <v>-412.57000000000346</v>
       </c>
       <c r="D4">
-        <v>-939.47000000004732</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-515.09000000000231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="B5" s="2">
-        <v>-901.45000000003893</v>
+        <v>-413.07499999999658</v>
       </c>
       <c r="C5">
-        <v>-901.45000000003893</v>
+        <v>-405.99000000000115</v>
       </c>
       <c r="D5">
-        <v>-883.75000000004809</v>
+        <v>-509.91000000000281</v>
       </c>
       <c r="E5">
-        <v>-883.75000000004809</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-501.74000000000245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="B6" s="2">
-        <v>-850.31000000003053</v>
+        <v>-413.07499999999658</v>
       </c>
       <c r="C6">
-        <v>-850.31000000003053</v>
+        <v>-405.99000000000115</v>
       </c>
       <c r="D6">
-        <v>-832.61000000003958</v>
+        <v>-509.91000000000281</v>
       </c>
       <c r="E6">
-        <v>-832.61000000003958</v>
+        <v>-501.74000000000262</v>
       </c>
       <c r="F6">
-        <v>-943.20000000003267</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-501.74000000000251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="B7" s="2">
-        <v>-819.83000000003074</v>
+        <v>-413.07499999999658</v>
       </c>
       <c r="C7">
-        <v>-819.83000000003074</v>
+        <v>-405.9900000000012</v>
       </c>
       <c r="D7">
-        <v>-802.1300000000399</v>
+        <v>-509.91000000000281</v>
       </c>
       <c r="E7">
-        <v>-802.13000000003967</v>
+        <v>-501.74000000000262</v>
       </c>
       <c r="F7">
-        <v>-912.720000000033</v>
+        <v>-501.74000000000245</v>
       </c>
       <c r="G7">
-        <v>-795.6600000000301</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-501.74000000000251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="B8" s="2">
-        <v>-785.70000000002938</v>
+        <v>-297.59000000001583</v>
       </c>
       <c r="C8">
-        <v>-785.70000000002938</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="D8">
-        <v>-768.00000000003865</v>
+        <v>-393.24000000000194</v>
       </c>
       <c r="E8">
-        <v>-768.00000000003854</v>
+        <v>-385.07000000000158</v>
       </c>
       <c r="F8">
-        <v>-860.46000000003164</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="G8">
-        <v>-743.40000000002897</v>
+        <v>-385.07000000000158</v>
       </c>
       <c r="H8">
-        <v>-760.97500000002151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-399.46500000001203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="B9" s="2">
-        <v>-704.36000000001422</v>
+        <v>-297.59000000001589</v>
       </c>
       <c r="C9">
-        <v>-704.36000000001422</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="D9">
-        <v>-686.66000000002327</v>
+        <v>-393.24000000000188</v>
       </c>
       <c r="E9">
-        <v>-686.66000000002327</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="F9">
-        <v>-779.12000000001638</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="G9">
-        <v>-662.06000000001359</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="H9">
-        <v>-668.1150000000066</v>
+        <v>-291.24500000001399</v>
       </c>
       <c r="I9">
-        <v>-690.14500000002704</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-291.24500000001399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="B10" s="2">
-        <v>-730.14999999999793</v>
+        <v>-297.59000000001595</v>
       </c>
       <c r="C10">
-        <v>-730.14999999999793</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="D10">
-        <v>-609.96999999998661</v>
+        <v>-393.24000000000194</v>
       </c>
       <c r="E10">
-        <v>-609.96999999998673</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="F10">
-        <v>-702.42999999997983</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="G10">
-        <v>-568.31000000000154</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="H10">
-        <v>-570.93499999999472</v>
+        <v>-291.24500000001387</v>
       </c>
       <c r="I10">
-        <v>-570.93499999999483</v>
+        <v>-291.24500000001399</v>
       </c>
       <c r="J10">
-        <v>-562.22999999999297</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>-291.24500000001399</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1E-3</v>
       </c>
       <c r="B11" s="2">
-        <v>-697.46999999998388</v>
+        <v>-297.59000000001589</v>
       </c>
       <c r="C11">
-        <v>-697.46999999998411</v>
+        <v>-290.50500000002046</v>
       </c>
       <c r="D11">
-        <v>-577.28999999997268</v>
+        <v>-393.24000000000194</v>
       </c>
       <c r="E11">
-        <v>-577.28999999997257</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="F11">
-        <v>-576.55999999998403</v>
+        <v>-385.07000000000164</v>
       </c>
       <c r="G11">
-        <v>-529.65499999999747</v>
+        <v>-385.07000000000153</v>
       </c>
       <c r="H11">
-        <v>-532.27999999999076</v>
+        <v>-291.24500000001382</v>
       </c>
       <c r="I11">
-        <v>-532.27999999999065</v>
+        <v>-291.24500000001382</v>
       </c>
       <c r="J11">
-        <v>-532.27999999999065</v>
+        <v>-291.24500000001387</v>
       </c>
       <c r="K11">
-        <v>-361.18499999999784</v>
+        <v>-291.24500000001387</v>
       </c>
     </row>
   </sheetData>
